--- a/central_eprocure.xlsx
+++ b/central_eprocure.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>142.</t>
+          <t>164.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1392.</t>
+          <t>1406.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/central_eprocure.xlsx
+++ b/central_eprocure.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>164.</t>
+          <t>244.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1406.</t>
+          <t>1375.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/central_eprocure.xlsx
+++ b/central_eprocure.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>244.</t>
+          <t>364.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1375.</t>
+          <t>1488.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/central_eprocure.xlsx
+++ b/central_eprocure.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>364.</t>
+          <t>548.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1488.</t>
+          <t>1605.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/central_eprocure.xlsx
+++ b/central_eprocure.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>548.</t>
+          <t>933.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1605.</t>
+          <t>1807.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/central_eprocure.xlsx
+++ b/central_eprocure.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>933.</t>
+          <t>940.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1807.</t>
+          <t>1812.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/central_eprocure.xlsx
+++ b/central_eprocure.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>940.</t>
+          <t>1108.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1812.</t>
+          <t>1964.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/central_eprocure.xlsx
+++ b/central_eprocure.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1108.</t>
+          <t>1110.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1964.</t>
+          <t>1966.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/central_eprocure.xlsx
+++ b/central_eprocure.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1110.</t>
+          <t>1228.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1966.</t>
+          <t>2037.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/central_eprocure.xlsx
+++ b/central_eprocure.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1228.</t>
+          <t>1285.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2037.</t>
+          <t>2010.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/central_eprocure.xlsx
+++ b/central_eprocure.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1285.</t>
+          <t>1367.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2010.</t>
+          <t>2078.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/central_eprocure.xlsx
+++ b/central_eprocure.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Captured Backup</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -490,105 +490,47 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1367.</t>
+          <t>2095.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:00 PM</t>
+          <t>03-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>24-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:30 AM</t>
+          <t>25-Jun-2026 06:05 PM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
+          <t>[Comprehensive Annual Repair Maintenance and Operations (ARMO) of ESIC Hospital and Staff Quarters at Kala Amb, Distt-Sirmour, HP- during 2026-27.] [W-17/1/2026/RO-PMD-Misc][2026_ESIC_911422_1]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
+          <t>Employees State Insurance Corporation||R.O. Himachal Pradesh</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3,18,03,649</t>
+          <t>1,30,03,957</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>31803649</v>
+        <v>13003957</v>
       </c>
       <c r="L2" t="inlineStr">
-        <is>
-          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Central eProcure</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2078.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>03-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>24-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>25-Jun-2026 06:05 PM</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>[Comprehensive Annual Repair Maintenance and Operations (ARMO) of ESIC Hospital and Staff Quarters at Kala Amb, Distt-Sirmour, HP- during 2026-27.] [W-17/1/2026/RO-PMD-Misc][2026_ESIC_911422_1]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Employees State Insurance Corporation||R.O. Himachal Pradesh</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1,30,03,957</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>13003957</v>
-      </c>
-      <c r="L3" t="inlineStr">
         <is>
           <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc6oEKlA0tALrMKwrkHr0%2Fg%3D%3D</t>
         </is>

--- a/central_eprocure.xlsx
+++ b/central_eprocure.xlsx
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Review Tender</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -490,49 +490,49 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2095.</t>
+          <t>1283.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>03-Jun-2026 06:00 PM</t>
+          <t>19-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24-Jun-2026 06:00 PM</t>
+          <t>18-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>25-Jun-2026 06:05 PM</t>
+          <t>20-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[Comprehensive Annual Repair Maintenance and Operations (ARMO) of ESIC Hospital and Staff Quarters at Kala Amb, Distt-Sirmour, HP- during 2026-27.] [W-17/1/2026/RO-PMD-Misc][2026_ESIC_911422_1]</t>
+          <t>[Major Civil Repairs Work at Administrative Block Building, AJNIFM Campus, Sector-48, Faridabad (Haryana)] [AJNIFM/Civil/2026-27/02][2026_DEXP_913889_1]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Employees State Insurance Corporation||R.O. Himachal Pradesh</t>
+          <t>Department of Expenditure||National Institute of Financial Management,DoE,MoF||Administration-NIFM - DOE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1,30,03,957</t>
+          <t>1,60,53,363</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>13003957</v>
+        <v>16053363</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc6oEKlA0tALrMKwrkHr0%2Fg%3D%3D</t>
+          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqLIcR0oNNfX%2FttiKnGHdeQ%3D%3D</t>
         </is>
       </c>
     </row>
